--- a/basedatos_partidas/salida/descompuestos/09.07.01.010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/09.07.01.010.xlsx
@@ -558,10 +558,10 @@
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>39.2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>106.8</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="18">
@@ -925,10 +925,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>138.57</v>
+        <v>143.37</v>
       </c>
       <c r="H28" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="29">
@@ -944,7 +944,7 @@
       </c>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="5" t="n">
-        <v>139.96</v>
+        <v>144.8</v>
       </c>
     </row>
   </sheetData>
